--- a/AAE 450 Master Sheet.xlsx
+++ b/AAE 450 Master Sheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/beda079effa9abdf/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eraybass/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF822D89-1DF3-4E6B-97A1-8D78BE1A1C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09EE66F-5306-6246-9E04-61BB2DFBC61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="3" activeTab="6" xr2:uid="{7704688C-A063-4A59-BE96-2C985B8200F6}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="19420" windowHeight="11020" xr2:uid="{7704688C-A063-4A59-BE96-2C985B8200F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Systems" sheetId="1" r:id="rId1"/>
@@ -42,6 +42,14 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>Hi This is elijah</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -411,9 +419,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29751829-E64D-4C4B-84A1-9B2B18C1AE39}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <dimension ref="C10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="10" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -421,7 +435,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22779F5B-D7AD-4F66-9DF1-373E1B44AF1E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -430,7 +444,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F5877D-8BDC-44C4-87CC-436238A2E44D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -439,7 +453,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED7A508-67D7-45F4-BE2F-43532227F3AB}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -448,7 +462,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{313FB50E-BF24-4F24-BF40-154503490985}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -457,7 +471,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80D363F9-67D2-4F46-8F45-0953B7339E99}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -466,7 +480,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE35D33F-F048-445A-B768-FEA6EDE3C4DE}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
